--- a/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T10:06:59+00:00</t>
+    <t>2026-08-20T14:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -347,7 +347,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260716085851</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}

--- a/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T14:37:13+00:00</t>
+    <t>2026-08-25T08:25:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T08:25:54+00:00</t>
+    <t>2026-08-25T13:09:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:09:33+00:00</t>
+    <t>2026-08-25T13:40:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:40:20+00:00</t>
+    <t>2026-08-25T14:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T14:52:49+00:00</t>
+    <t>2026-08-26T13:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:43:53+00:00</t>
+    <t>2026-08-26T14:38:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T14:38:07+00:00</t>
+    <t>2026-08-27T07:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
